--- a/registration_forms/038_soccer_financial_aid_agreement--registration_forms.xlsx
+++ b/registration_forms/038_soccer_financial_aid_agreement--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>soccer</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Soccer</t>
+          <t>Hockey</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>track_and_field</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hockey</t>
+          <t>Track and Field</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>track_and_field</t>
+          <t>golf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Track and Field</t>
+          <t>Golf</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>golf</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Tennis</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>wrestling</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Wrestling</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>wrestling</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wrestling</t>
+          <t>Volleyball</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>softball</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Volleyball</t>
+          <t>Softball</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>softball</t>
+          <t>cross_country</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Softball</t>
+          <t>Cross Country</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cross_country</t>
+          <t>swimming</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cross Country</t>
+          <t>Swimming</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>swimming</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Swimming</t>
+          <t>Rugby</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>soccer</t>
+          <t>dance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Soccer</t>
+          <t>Dance</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rugby</t>
+          <t>gymnastics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rugby</t>
+          <t>Gymnastics</t>
         </is>
       </c>
     </row>
@@ -1029,233 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dance</t>
+          <t>rowing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dance</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>gymnastics</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Gymnastics</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>rowing</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>Rowing</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Soccer</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>financial_aid_request_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>soccer</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Soccer</t>
         </is>
       </c>
     </row>
